--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:46</t>
+    <t xml:space="preserve">2026-10-05 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -696,7 +696,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>615136.62</v>
+        <v>615136.63</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>572992.12</v>
+        <v>572992.13</v>
       </c>
     </row>
     <row r="21">
@@ -934,7 +934,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>552984.12</v>
+        <v>552984.13</v>
       </c>
     </row>
     <row r="24">
@@ -985,7 +985,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>543095.62</v>
+        <v>543095.63</v>
       </c>
     </row>
     <row r="27">
